--- a/conditions/blocks.xlsx
+++ b/conditions/blocks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Psychopy\Experiments\AX_CPT\AX_CPT_baseline\conditions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF57330E-DB6E-4528-88DF-6637B1D64A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B82710-69D3-48C2-AC78-34D4D71C717E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,13 +30,13 @@
     <t>block_rows</t>
   </si>
   <si>
-    <t>72:144</t>
+    <t>0:2</t>
   </si>
   <si>
-    <t>144:216</t>
+    <t>72:74</t>
   </si>
   <si>
-    <t>0:72</t>
+    <t>144:146</t>
   </si>
 </sst>
 </file>
@@ -365,17 +365,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
